--- a/Raster.logic.xlsx
+++ b/Raster.logic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\KE.beef.spatial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BF221E-B359-443A-A71F-878D38DA2E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0911EB43-0D8F-4A35-85AD-1221D7D9E630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{E8C4D828-59A7-4D6B-8FA1-BE0758A76F31}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{E8C4D828-59A7-4D6B-8FA1-BE0758A76F31}"/>
   </bookViews>
   <sheets>
     <sheet name="Raster_logic" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="87">
   <si>
     <t>Finisher Boran</t>
   </si>
@@ -285,6 +285,24 @@
   </si>
   <si>
     <t>NPP_SHRUB_2050_R4.tif</t>
+  </si>
+  <si>
+    <t>NPP_CROP_2050_R8.tif</t>
+  </si>
+  <si>
+    <t>NPP_GRASS_2050_R8.tif</t>
+  </si>
+  <si>
+    <t>NPP_SHRUB_2050_R8.tif</t>
+  </si>
+  <si>
+    <t>("MODIS_NPP_2050_R8_new_new@1")*("2020_LC_LR_is_grassland@1"=1)</t>
+  </si>
+  <si>
+    <t>("MODIS_NPP_2050_R8_new_new@1")*("2020_LC_LR_is_cropland@1"=1)</t>
+  </si>
+  <si>
+    <t>("MODIS_NPP_2050_R8_new_new@1")*("2020_LC_LR_is_shrubland@1"=1)</t>
   </si>
 </sst>
 </file>
@@ -349,7 +367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -361,6 +379,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1145,7 +1169,7 @@
       <c r="E54" s="4" t="str">
         <f>_xlfn.CONCAT("('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*((",I54,")*(",G54,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*((",J54,")*(",G54,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*((",K54,")*(",G54,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=6)*((",L54,")*(",G54,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*((",M54,")*(",G54,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*((",N54,")*(",G54,")+1)
 ")</f>
-        <v xml:space="preserve">('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*((0.104166666666667)*(0.16667)+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*((0)*(0.16667)+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*((-0.0952380952380953)*(0.16667)+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=6)*((0.0212765957446808)*(0.16667)+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*((-0.0599999999999999)*(0.16667)+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*((-0.168421052631579)*(0.16667)+1)
+        <v xml:space="preserve">('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*((0.104166666666667)*(0.16667)+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*((0)*(0.16667)+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*((-0.0952380952380953)*(0.16667)+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=6)*((0.0212765957446808)*(0.16667)+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*((-0.0599999999999999)*(0.16667)+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*((-0.126315789473684)*(0.16667)+1)
 </v>
       </c>
       <c r="F54" t="s">
@@ -1176,7 +1200,7 @@
       </c>
       <c r="N54">
         <f t="shared" si="0"/>
-        <v>-0.16842105263157892</v>
+        <v>-0.12631578947368416</v>
       </c>
     </row>
     <row r="55" spans="4:14" ht="126" customHeight="1" x14ac:dyDescent="0.25">
@@ -1186,7 +1210,7 @@
       <c r="E55" s="4" t="str">
         <f>_xlfn.CONCAT("('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*(",I55,") +('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*(",J55,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*(",K55,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=6)*(",L55,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(",M55,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*(",N55,") 
 ")</f>
-        <v xml:space="preserve">('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*(1.10416666666667) +('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*(1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*(0.904761904761905)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=6)*(1.02127659574468)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(0.94)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*(0.831578947368421) 
+        <v xml:space="preserve">('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*(1.10416666666667) +('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*(1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*(0.904761904761905)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=6)*(1.02127659574468)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(0.94)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*(0.873684210526316) 
 </v>
       </c>
       <c r="H55" t="s">
@@ -1212,8 +1236,8 @@
         <v>0.94000000000000006</v>
       </c>
       <c r="N55">
-        <f>7.9/9.5</f>
-        <v>0.83157894736842108</v>
+        <f>8.3/9.5</f>
+        <v>0.87368421052631584</v>
       </c>
     </row>
     <row r="56" spans="4:14" ht="60" x14ac:dyDescent="0.25">
@@ -1223,7 +1247,7 @@
       <c r="E56" s="4" t="str">
         <f>_xlfn.CONCAT("('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*(",I56,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*(",J56,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*(",K56,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(",L56,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(",M56,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*(",N56,") ) 
 ")</f>
-        <v xml:space="preserve">('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*(1.175)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*(1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*(1.28813559322034)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(1.01063829787234)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(0.86)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*(0.926315789473684) ) 
+        <v xml:space="preserve">('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*(1.175)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*(1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*(0.892857142857143)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(1.01063829787234)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(0.86)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*(0.863157894736842) ) 
 </v>
       </c>
       <c r="H56" t="s">
@@ -1237,8 +1261,8 @@
         <v>1</v>
       </c>
       <c r="K56">
-        <f>3.8/2.95</f>
-        <v>1.2881355932203389</v>
+        <f>3.75/4.2</f>
+        <v>0.89285714285714279</v>
       </c>
       <c r="L56">
         <f>4.75/4.7</f>
@@ -1249,8 +1273,8 @@
         <v>0.86</v>
       </c>
       <c r="N56">
-        <f>8.8/9.5</f>
-        <v>0.92631578947368431</v>
+        <f>8.2/9.5</f>
+        <v>0.86315789473684201</v>
       </c>
     </row>
     <row r="57" spans="4:14" ht="84" customHeight="1" x14ac:dyDescent="0.25">
@@ -1347,15 +1371,33 @@
       <c r="D74" s="3" t="s">
         <v>55</v>
       </c>
+      <c r="E74" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F74" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="75" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D75" s="3" t="s">
         <v>56</v>
       </c>
+      <c r="E75" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F75" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="76" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D76" s="3" t="s">
         <v>57</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="F76" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="77" spans="4:9" x14ac:dyDescent="0.25">

--- a/Raster.logic.xlsx
+++ b/Raster.logic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\KE.beef.spatial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0911EB43-0D8F-4A35-85AD-1221D7D9E630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B06969-DB84-4F56-AC22-6F2F291D22E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{E8C4D828-59A7-4D6B-8FA1-BE0758A76F31}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="90">
   <si>
     <t>Finisher Boran</t>
   </si>
@@ -263,15 +263,6 @@
     <t>2050 R8</t>
   </si>
   <si>
-    <t>("NPP_2020@1")*("2020_LC_LR_is_grassland@1"=1)</t>
-  </si>
-  <si>
-    <t>("NPP_2020@1")*("2020_LC_LR_is_cropland@1"=1)</t>
-  </si>
-  <si>
-    <t>("NPP_2020@1")*("2020_LC_LR_is_shrubland@1"=1)</t>
-  </si>
-  <si>
     <t>("MODIS_NPP_2050_R4_new@1")*("2020_LC_LR_is_grassland@1"=1)</t>
   </si>
   <si>
@@ -303,6 +294,24 @@
   </si>
   <si>
     <t>("MODIS_NPP_2050_R8_new_new@1")*("2020_LC_LR_is_shrubland@1"=1)</t>
+  </si>
+  <si>
+    <t>("MODIS_NPP_2020_New@1")*("2020_LC_LR_is_grassland@1"=1)</t>
+  </si>
+  <si>
+    <t>("MODIS_NPP_2020_New@1")*("2020_LC_LR_is_cropland@1"=1)</t>
+  </si>
+  <si>
+    <t>("MODIS_NPP_2020_New@1")*("2020_LC_LR_is_shrubland@1"=1)</t>
+  </si>
+  <si>
+    <t>NPP_2020_CROP_new</t>
+  </si>
+  <si>
+    <t>NPP_2020_GRASS_new</t>
+  </si>
+  <si>
+    <t>NPP_2020_SHRUB_new</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1311,10 @@
         <v>55</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>73</v>
+        <v>84</v>
+      </c>
+      <c r="F64" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="65" spans="4:9" x14ac:dyDescent="0.25">
@@ -1310,7 +1322,10 @@
         <v>56</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>74</v>
+        <v>85</v>
+      </c>
+      <c r="F65" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="4:9" x14ac:dyDescent="0.25">
@@ -1318,7 +1333,10 @@
         <v>57</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>75</v>
+        <v>86</v>
+      </c>
+      <c r="F66" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="4:9" x14ac:dyDescent="0.25">
@@ -1334,7 +1352,7 @@
         <v>55</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70" spans="4:9" x14ac:dyDescent="0.25">
@@ -1342,10 +1360,10 @@
         <v>56</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F70" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71" spans="4:9" x14ac:dyDescent="0.25">
@@ -1353,10 +1371,10 @@
         <v>57</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F71" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="4:9" x14ac:dyDescent="0.25">
@@ -1372,10 +1390,10 @@
         <v>55</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F74" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="75" spans="4:9" x14ac:dyDescent="0.25">
@@ -1383,10 +1401,10 @@
         <v>56</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F75" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="4:9" x14ac:dyDescent="0.25">
@@ -1394,10 +1412,10 @@
         <v>57</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F76" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="77" spans="4:9" x14ac:dyDescent="0.25">

--- a/Raster.logic.xlsx
+++ b/Raster.logic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\KE.beef.spatial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B06969-DB84-4F56-AC22-6F2F291D22E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99BDFFE-26A3-49E1-AC51-D839D84E147A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{E8C4D828-59A7-4D6B-8FA1-BE0758A76F31}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E8C4D828-59A7-4D6B-8FA1-BE0758A76F31}"/>
   </bookViews>
   <sheets>
     <sheet name="Raster_logic" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="91">
   <si>
     <t>Finisher Boran</t>
   </si>
@@ -155,9 +155,6 @@
     <t>AGBR Grass</t>
   </si>
   <si>
-    <t>PUF Grass</t>
-  </si>
-  <si>
     <t>Crop biomass</t>
   </si>
   <si>
@@ -312,6 +309,12 @@
   </si>
   <si>
     <t>NPP_2020_SHRUB_new</t>
+  </si>
+  <si>
+    <t>PUF Grass -- grassland -- extensive</t>
+  </si>
+  <si>
+    <t>PUF Grass -- grassland -- intensive</t>
   </si>
 </sst>
 </file>
@@ -780,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{589F234B-56A4-4CB3-B68D-D99D514D570A}">
-  <dimension ref="B2:N99"/>
+  <dimension ref="B2:N100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="28.42578125" customWidth="1"/>
@@ -1150,30 +1153,30 @@
     </row>
     <row r="53" spans="4:14" x14ac:dyDescent="0.25">
       <c r="E53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J53" t="s">
+        <v>63</v>
+      </c>
+      <c r="K53" t="s">
+        <v>62</v>
+      </c>
+      <c r="L53" t="s">
         <v>64</v>
       </c>
-      <c r="K53" t="s">
-        <v>63</v>
-      </c>
-      <c r="L53" t="s">
+      <c r="M53" t="s">
         <v>65</v>
       </c>
-      <c r="M53" t="s">
+      <c r="N53" t="s">
         <v>66</v>
-      </c>
-      <c r="N53" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="54" spans="4:14" ht="75" x14ac:dyDescent="0.25">
       <c r="D54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E54" s="4" t="str">
         <f>_xlfn.CONCAT("('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*((",I54,")*(",G54,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*((",J54,")*(",G54,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*((",K54,")*(",G54,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=6)*((",L54,")*(",G54,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*((",M54,")*(",G54,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*((",N54,")*(",G54,")+1)
@@ -1182,7 +1185,7 @@
 </v>
       </c>
       <c r="F54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G54">
         <v>0.16667000000000001</v>
@@ -1223,7 +1226,7 @@
 </v>
       </c>
       <c r="H55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I55">
         <f>26.5/24</f>
@@ -1260,7 +1263,7 @@
 </v>
       </c>
       <c r="H56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I56">
         <f>28.2/24</f>
@@ -1298,7 +1301,7 @@
     <row r="62" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D62" s="3"/>
       <c r="E62" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63" spans="4:14" x14ac:dyDescent="0.25">
@@ -1308,35 +1311,35 @@
     </row>
     <row r="64" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D64" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F64" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D65" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D66" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F66" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="4:9" x14ac:dyDescent="0.25">
@@ -1344,37 +1347,37 @@
     </row>
     <row r="68" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D68" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D69" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D70" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F70" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D71" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="72" spans="4:9" x14ac:dyDescent="0.25">
@@ -1382,40 +1385,40 @@
     </row>
     <row r="73" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D73" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D74" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D75" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F75" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D76" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F76" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77" spans="4:9" x14ac:dyDescent="0.25">
@@ -1426,7 +1429,7 @@
         <v>34</v>
       </c>
       <c r="E79" t="str">
-        <f>_xlfn.CONCAT("'MODIS_2020_ALL_final@1'*(((2020_LC_is_grassland@1=1)*(",I83,"))+((2020_LC_is_cropland@1=1)(",I84,"))+((2020_LC_is_shrubland@1=1)*(",I85,")))*(",I79,")*(",I80,")*(",I81,")")</f>
+        <f>_xlfn.CONCAT("'MODIS_2020_ALL_final@1'*(((2020_LC_is_grassland@1=1)*(",I84,"))+((2020_LC_is_cropland@1=1)(",I85,"))+((2020_LC_is_shrubland@1=1)*(",I86,")))*(",I79,")*(",I80,")*(",I81,")")</f>
         <v>'MODIS_2020_ALL_final@1'*(((2020_LC_is_grassland@1=1)*(1))+((2020_LC_is_cropland@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.3)</v>
       </c>
       <c r="H79" t="s">
@@ -1448,86 +1451,84 @@
     <row r="81" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D81" s="3"/>
       <c r="H81" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="I81">
         <v>0.3</v>
       </c>
     </row>
     <row r="82" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D82" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E82" t="str">
-        <f>_xlfn.CONCAT("'MODIS_2020_ALL_final@1'*(((2020_LC_is_cropland@1=1)*(",I91,")))*(",I87,")*(",I88,")*(",I89,")")</f>
+      <c r="D82" s="3"/>
+      <c r="H82" t="s">
+        <v>90</v>
+      </c>
+      <c r="I82">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="83" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D83" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E83" t="str">
+        <f>_xlfn.CONCAT("'MODIS_2020_ALL_final@1'*(((2020_LC_is_cropland@1=1)*(",I92,")))*(",I88,")*(",I89,")*(",I90,")")</f>
         <v>'MODIS_2020_ALL_final@1'*(((2020_LC_is_cropland@1=1)*(0.4)))*(0.4)*(0.5)*(0.5)</v>
-      </c>
-    </row>
-    <row r="83" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D83" s="3"/>
-      <c r="H83" t="s">
-        <v>39</v>
-      </c>
-      <c r="I83" s="5">
-        <v>1</v>
       </c>
     </row>
     <row r="84" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D84" s="3"/>
       <c r="H84" t="s">
+        <v>38</v>
+      </c>
+      <c r="I84" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D85" s="3"/>
+      <c r="H85" t="s">
+        <v>39</v>
+      </c>
+      <c r="I85" s="5">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="86" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D86" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I84" s="5">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="85" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D85" s="3" t="s">
+      <c r="E86" t="s">
         <v>41</v>
       </c>
-      <c r="E85" t="s">
+      <c r="H86" t="s">
         <v>42</v>
       </c>
-      <c r="H85" t="s">
+      <c r="I86" s="5">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="87" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H87" t="s">
+        <v>58</v>
+      </c>
+      <c r="I87" s="5">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="88" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D88" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I85" s="5">
+      <c r="H88" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I88" s="5">
         <v>0.4</v>
       </c>
     </row>
-    <row r="86" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H86" t="s">
-        <v>59</v>
-      </c>
-      <c r="I86" s="5">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="87" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D87" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H87" s="6" t="s">
+    <row r="89" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H89" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="I87" s="5">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="88" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H88" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="I88" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="89" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D89" t="s">
-        <v>47</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="I89" s="5">
         <v>0.5</v>
@@ -1535,68 +1536,79 @@
     </row>
     <row r="90" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D90" t="s">
-        <v>49</v>
-      </c>
-      <c r="E90" t="str">
-        <f>_xlfn.CONCAT("'MODIS_NPP_2050_R4@1'*(((2020_LC_is_grassland@1=1)*(",I83,"))+((2020_LC_is_cropland@1=1)(",I84,"))+((2020_LC_is_shrubland@1=1)*(",I85,")))*(",I79,")*(",I80,")*(",I81,")")</f>
-        <v>'MODIS_NPP_2050_R4@1'*(((2020_LC_is_grassland@1=1)*(1))+((2020_LC_is_cropland@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.3)</v>
+        <v>46</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I90" s="5">
+        <v>0.5</v>
       </c>
     </row>
     <row r="91" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D91" t="s">
+        <v>48</v>
+      </c>
+      <c r="E91" t="str">
+        <f>_xlfn.CONCAT("'MODIS_NPP_2050_R4@1'*(((2020_LC_is_grassland@1=1)*(",I84,"))+((2020_LC_is_cropland@1=1)(",I85,"))+((2020_LC_is_shrubland@1=1)*(",I86,")))*(",I79,")*(",I80,")*(",I81,")")</f>
+        <v>'MODIS_NPP_2050_R4@1'*(((2020_LC_is_grassland@1=1)*(1))+((2020_LC_is_cropland@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.3)</v>
+      </c>
+    </row>
+    <row r="92" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
+        <v>49</v>
+      </c>
+      <c r="E92" t="str">
+        <f>_xlfn.CONCAT("'MODIS_NPP_2050_R8@1'*(((2020_LC_is_grassland)*(",I84,"))+((E75@1=1)(",I85,"))+((2020_LC_is_shrubland@1=1)*(",I86,")))*(",I79,")*(",I80,")*(",I81,")")</f>
+        <v>'MODIS_NPP_2050_R8@1'*(((2020_LC_is_grassland)*(1))+((E75@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.3)</v>
+      </c>
+      <c r="H92" t="s">
         <v>50</v>
       </c>
-      <c r="E91" t="str">
-        <f>_xlfn.CONCAT("'MODIS_NPP_2050_R8@1'*(((2020_LC_is_grassland)*(",I83,"))+((E75@1=1)(",I84,"))+((2020_LC_is_shrubland@1=1)*(",I85,")))*(",I79,")*(",I80,")*(",I81,")")</f>
-        <v>'MODIS_NPP_2050_R8@1'*(((2020_LC_is_grassland)*(1))+((E75@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.3)</v>
-      </c>
-      <c r="H91" t="s">
-        <v>51</v>
-      </c>
-      <c r="I91" s="5">
+      <c r="I92" s="5">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="93" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D93" t="s">
-        <v>52</v>
-      </c>
-      <c r="I93" s="5"/>
     </row>
     <row r="94" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D94" t="s">
-        <v>49</v>
-      </c>
-      <c r="E94" t="str">
-        <f>_xlfn.CONCAT("'MODIS_NPP_2050_R4@1'*(((2020_LC_is_cropland@1=1)*(",I91,")))*(",I87,")*(",I88,")*(",I89,")")</f>
-        <v>'MODIS_NPP_2050_R4@1'*(((2020_LC_is_cropland@1=1)*(0.4)))*(0.4)*(0.5)*(0.5)</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I94" s="5"/>
     </row>
     <row r="95" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D95" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E95" t="str">
-        <f>_xlfn.CONCAT("'MODIS_NPP_2050_R8@1'*(((2020_LC_is_cropland@1=1)*(",I91,")))*(",I87,")*(",I88,")*(",I89,")")</f>
+        <f>_xlfn.CONCAT("'MODIS_NPP_2050_R4@1'*(((2020_LC_is_cropland@1=1)*(",I92,")))*(",I88,")*(",I89,")*(",I90,")")</f>
+        <v>'MODIS_NPP_2050_R4@1'*(((2020_LC_is_cropland@1=1)*(0.4)))*(0.4)*(0.5)*(0.5)</v>
+      </c>
+    </row>
+    <row r="96" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>49</v>
+      </c>
+      <c r="E96" t="str">
+        <f>_xlfn.CONCAT("'MODIS_NPP_2050_R8@1'*(((2020_LC_is_cropland@1=1)*(",I92,")))*(",I88,")*(",I89,")*(",I90,")")</f>
         <v>'MODIS_NPP_2050_R8@1'*(((2020_LC_is_cropland@1=1)*(0.4)))*(0.4)*(0.5)*(0.5)</v>
       </c>
     </row>
-    <row r="97" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D97" s="3" t="s">
+    <row r="98" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D98" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E98" t="s">
         <v>41</v>
-      </c>
-      <c r="E97" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="98" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D98" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="99" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D99" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="100" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/Raster.logic.xlsx
+++ b/Raster.logic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\KE.beef.spatial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99BDFFE-26A3-49E1-AC51-D839D84E147A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94719179-A1B6-49A9-BFCD-FB3553C88365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E8C4D828-59A7-4D6B-8FA1-BE0758A76F31}"/>
   </bookViews>
@@ -353,7 +353,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -363,6 +363,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -379,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -399,6 +405,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -426,15 +434,11 @@
     <sheetNames>
       <sheetName val="Model_implemented"/>
       <sheetName val="FAO_2019_animal_trends"/>
-      <sheetName val="Raster_logic"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="35">
-          <cell r="F35">
-            <v>0.53615960099750615</v>
-          </cell>
           <cell r="G35">
             <v>0.38312009613345605</v>
           </cell>
@@ -460,7 +464,6 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1430,7 +1433,7 @@
       </c>
       <c r="E79" t="str">
         <f>_xlfn.CONCAT("'MODIS_2020_ALL_final@1'*(((2020_LC_is_grassland@1=1)*(",I84,"))+((2020_LC_is_cropland@1=1)(",I85,"))+((2020_LC_is_shrubland@1=1)*(",I86,")))*(",I79,")*(",I80,")*(",I81,")")</f>
-        <v>'MODIS_2020_ALL_final@1'*(((2020_LC_is_grassland@1=1)*(1))+((2020_LC_is_cropland@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.3)</v>
+        <v>'MODIS_2020_ALL_final@1'*(((2020_LC_is_grassland@1=1)*(1))+((2020_LC_is_cropland@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.365)</v>
       </c>
       <c r="H79" t="s">
         <v>35</v>
@@ -1453,8 +1456,8 @@
       <c r="H81" t="s">
         <v>89</v>
       </c>
-      <c r="I81">
-        <v>0.3</v>
+      <c r="I81" s="12">
+        <v>0.36499999999999999</v>
       </c>
     </row>
     <row r="82" spans="4:9" x14ac:dyDescent="0.25">
@@ -1462,8 +1465,8 @@
       <c r="H82" t="s">
         <v>90</v>
       </c>
-      <c r="I82">
-        <v>0.45</v>
+      <c r="I82" s="12">
+        <v>0.4</v>
       </c>
     </row>
     <row r="83" spans="4:9" x14ac:dyDescent="0.25">
@@ -1472,7 +1475,7 @@
       </c>
       <c r="E83" t="str">
         <f>_xlfn.CONCAT("'MODIS_2020_ALL_final@1'*(((2020_LC_is_cropland@1=1)*(",I92,")))*(",I88,")*(",I89,")*(",I90,")")</f>
-        <v>'MODIS_2020_ALL_final@1'*(((2020_LC_is_cropland@1=1)*(0.4)))*(0.4)*(0.5)*(0.5)</v>
+        <v>'MODIS_2020_ALL_final@1'*(((2020_LC_is_cropland@1=1)*(0.4)))*(0.4)*(0.5)*(0.7)</v>
       </c>
     </row>
     <row r="84" spans="4:9" x14ac:dyDescent="0.25">
@@ -1541,8 +1544,8 @@
       <c r="H90" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I90" s="5">
-        <v>0.5</v>
+      <c r="I90" s="11">
+        <v>0.7</v>
       </c>
     </row>
     <row r="91" spans="4:9" x14ac:dyDescent="0.25">
@@ -1551,7 +1554,7 @@
       </c>
       <c r="E91" t="str">
         <f>_xlfn.CONCAT("'MODIS_NPP_2050_R4@1'*(((2020_LC_is_grassland@1=1)*(",I84,"))+((2020_LC_is_cropland@1=1)(",I85,"))+((2020_LC_is_shrubland@1=1)*(",I86,")))*(",I79,")*(",I80,")*(",I81,")")</f>
-        <v>'MODIS_NPP_2050_R4@1'*(((2020_LC_is_grassland@1=1)*(1))+((2020_LC_is_cropland@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.3)</v>
+        <v>'MODIS_NPP_2050_R4@1'*(((2020_LC_is_grassland@1=1)*(1))+((2020_LC_is_cropland@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.365)</v>
       </c>
     </row>
     <row r="92" spans="4:9" x14ac:dyDescent="0.25">
@@ -1560,7 +1563,7 @@
       </c>
       <c r="E92" t="str">
         <f>_xlfn.CONCAT("'MODIS_NPP_2050_R8@1'*(((2020_LC_is_grassland)*(",I84,"))+((E75@1=1)(",I85,"))+((2020_LC_is_shrubland@1=1)*(",I86,")))*(",I79,")*(",I80,")*(",I81,")")</f>
-        <v>'MODIS_NPP_2050_R8@1'*(((2020_LC_is_grassland)*(1))+((E75@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.3)</v>
+        <v>'MODIS_NPP_2050_R8@1'*(((2020_LC_is_grassland)*(1))+((E75@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.365)</v>
       </c>
       <c r="H92" t="s">
         <v>50</v>
@@ -1581,7 +1584,7 @@
       </c>
       <c r="E95" t="str">
         <f>_xlfn.CONCAT("'MODIS_NPP_2050_R4@1'*(((2020_LC_is_cropland@1=1)*(",I92,")))*(",I88,")*(",I89,")*(",I90,")")</f>
-        <v>'MODIS_NPP_2050_R4@1'*(((2020_LC_is_cropland@1=1)*(0.4)))*(0.4)*(0.5)*(0.5)</v>
+        <v>'MODIS_NPP_2050_R4@1'*(((2020_LC_is_cropland@1=1)*(0.4)))*(0.4)*(0.5)*(0.7)</v>
       </c>
     </row>
     <row r="96" spans="4:9" x14ac:dyDescent="0.25">
@@ -1590,7 +1593,7 @@
       </c>
       <c r="E96" t="str">
         <f>_xlfn.CONCAT("'MODIS_NPP_2050_R8@1'*(((2020_LC_is_cropland@1=1)*(",I92,")))*(",I88,")*(",I89,")*(",I90,")")</f>
-        <v>'MODIS_NPP_2050_R8@1'*(((2020_LC_is_cropland@1=1)*(0.4)))*(0.4)*(0.5)*(0.5)</v>
+        <v>'MODIS_NPP_2050_R8@1'*(((2020_LC_is_cropland@1=1)*(0.4)))*(0.4)*(0.5)*(0.7)</v>
       </c>
     </row>
     <row r="98" spans="4:5" x14ac:dyDescent="0.25">

--- a/Raster.logic.xlsx
+++ b/Raster.logic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\KE.beef.spatial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94719179-A1B6-49A9-BFCD-FB3553C88365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3E69B8-2678-4849-8F98-00CDF83450FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E8C4D828-59A7-4D6B-8FA1-BE0758A76F31}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="98">
   <si>
     <t>Finisher Boran</t>
   </si>
@@ -315,6 +315,27 @@
   </si>
   <si>
     <t>PUF Grass -- grassland -- intensive</t>
+  </si>
+  <si>
+    <t>Total biomass demand - 2020</t>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>WC</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
+  <si>
+    <t>(1/1000)*(1/100)*365*0.02*("Beef_density_total_adj_h_km2@1"*196.1 + "Sheep_density_total_h_km2@1" *30 + "Dairy_density_total_adj_h_km2@1"*201 )*( 1-0.065)</t>
+  </si>
+  <si>
+    <t>(1/1000)*(1/100)*365*0.02*("Beef_density_total_adj_h_km2@1"*194.3 + "Sheep_density_total_h_km2@1" *30 + "Dairy_density_total_adj_h_km2@1"*201 )*( 1-0.065)</t>
+  </si>
+  <si>
+    <t>(1/1000)*(1/100)*365*0.02*("Beef_density_total_adj_h_km2@1"*198.1 + "Sheep_density_total_h_km2@1" *30 + "Dairy_density_total_adj_h_km2@1"*201 )*( 1-0.065)</t>
   </si>
 </sst>
 </file>
@@ -786,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{589F234B-56A4-4CB3-B68D-D99D514D570A}">
-  <dimension ref="B2:N100"/>
+  <dimension ref="B2:N110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="28.42578125" customWidth="1"/>
@@ -945,672 +966,706 @@
         <v>('Beef_density_subs_adj_h_km2@1')*('Hybrid_AEZs@1'=3 OR 'Hybrid_AEZs@1'=4 OR 'Hybrid_AEZs@1'=5)*((0.0567))*((0.08))</v>
       </c>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D17" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D27" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
         <v>0</v>
       </c>
-      <c r="E19" t="str">
-        <f>_xlfn.CONCAT("'Finisher_Boran@1'+(30/100)*'Finisher_Boran@1'*(",G19,")")</f>
+      <c r="E29" t="str">
+        <f>_xlfn.CONCAT("'Finisher_Boran@1'+(30/100)*'Finisher_Boran@1'*(",G29,")")</f>
         <v>'Finisher_Boran@1'+(30/100)*'Finisher_Boran@1'*(86.4665653495441)</v>
       </c>
-      <c r="G19">
+      <c r="G29">
         <f>[1]FAO_2019_animal_trends!G37</f>
         <v>86.466565349544069</v>
       </c>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D20" t="s">
+    <row r="30" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
         <v>2</v>
       </c>
-      <c r="E20" t="str">
-        <f>_xlfn.CONCAT("'Finisher_Exotic@1'+(30/100)*'Finisher_Exotic@1'*(",G19,")")</f>
+      <c r="E30" t="str">
+        <f>_xlfn.CONCAT("'Finisher_Exotic@1'+(30/100)*'Finisher_Exotic@1'*(",G29,")")</f>
         <v>'Finisher_Exotic@1'+(30/100)*'Finisher_Exotic@1'*(86.4665653495441)</v>
       </c>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D21" t="s">
+    <row r="31" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
         <v>4</v>
       </c>
-      <c r="E21" t="str">
-        <f>_xlfn.CONCAT("'Cowcalf_Boran@1'+(30/100)*'Cowcalf_Boran@1'*(",G21,")")</f>
+      <c r="E31" t="str">
+        <f>_xlfn.CONCAT("'Cowcalf_Boran@1'+(30/100)*'Cowcalf_Boran@1'*(",G31,")")</f>
         <v>'Cowcalf_Boran@1'+(30/100)*'Cowcalf_Boran@1'*(1.03723404255319)</v>
       </c>
-      <c r="G21">
+      <c r="G31">
         <f>[1]FAO_2019_animal_trends!G38</f>
         <v>1.0372340425531916</v>
       </c>
     </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D22" t="s">
+    <row r="32" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
         <v>6</v>
       </c>
-      <c r="E22" t="str">
-        <f>_xlfn.CONCAT("'Cowcalf_Exotic@1'+(30/100)*'Cowcalf_Exotic@1'*(",G21,")")</f>
+      <c r="E32" t="str">
+        <f>_xlfn.CONCAT("'Cowcalf_Exotic@1'+(30/100)*'Cowcalf_Exotic@1'*(",G31,")")</f>
         <v>'Cowcalf_Exotic@1'+(30/100)*'Cowcalf_Exotic@1'*(1.03723404255319)</v>
       </c>
     </row>
-    <row r="24" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D24" t="s">
+    <row r="34" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
         <v>9</v>
       </c>
-      <c r="E24" t="str">
-        <f>_xlfn.CONCAT("'Pastoral_Zebu@1'+(30/100)*'Pastoral_Zebu@1'*(",G24,")")</f>
+      <c r="E34" t="str">
+        <f>_xlfn.CONCAT("'Pastoral_Zebu@1'+(30/100)*'Pastoral_Zebu@1'*(",G34,")")</f>
         <v>'Pastoral_Zebu@1'+(30/100)*'Pastoral_Zebu@1'*(0.383120096133456)</v>
       </c>
-      <c r="G24">
+      <c r="G34">
         <f>[1]FAO_2019_animal_trends!G35</f>
         <v>0.38312009613345605</v>
       </c>
     </row>
-    <row r="25" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D25" t="s">
+    <row r="35" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
         <v>11</v>
       </c>
-      <c r="E25" t="str">
-        <f>_xlfn.CONCAT("'Pastoral_Boran@1'+(30/100)*'Pastoral_Boran@1'*(",G24,")")</f>
+      <c r="E35" t="str">
+        <f>_xlfn.CONCAT("'Pastoral_Boran@1'+(30/100)*'Pastoral_Boran@1'*(",G34,")")</f>
         <v>'Pastoral_Boran@1'+(30/100)*'Pastoral_Boran@1'*(0.383120096133456)</v>
       </c>
     </row>
-    <row r="27" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D27" t="s">
+    <row r="37" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
         <v>13</v>
       </c>
-      <c r="E27" t="str">
-        <f>_xlfn.CONCAT("'Agpastoral_Zebu@1'+(30/100)*'Agpastoral_Zebu@1'*(",G27,")")</f>
+      <c r="E37" t="str">
+        <f>_xlfn.CONCAT("'Agpastoral_Zebu@1'+(30/100)*'Agpastoral_Zebu@1'*(",G37,")")</f>
         <v>'Agpastoral_Zebu@1'+(30/100)*'Agpastoral_Zebu@1'*(2.79504244838067)</v>
       </c>
-      <c r="G27">
+      <c r="G37">
         <f>[1]FAO_2019_animal_trends!G36</f>
         <v>2.7950424483806726</v>
       </c>
     </row>
-    <row r="28" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D28" t="s">
+    <row r="38" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
         <v>15</v>
       </c>
-      <c r="E28" t="str">
-        <f>_xlfn.CONCAT("'Agpastoral_Boran@1'+(30/100)*'Agpastoral_Boran@1'*(",G27,")")</f>
+      <c r="E38" t="str">
+        <f>_xlfn.CONCAT("'Agpastoral_Boran@1'+(30/100)*'Agpastoral_Boran@1'*(",G37,")")</f>
         <v>'Agpastoral_Boran@1'+(30/100)*'Agpastoral_Boran@1'*(2.79504244838067)</v>
       </c>
     </row>
-    <row r="30" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D30" t="s">
+    <row r="40" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
         <v>17</v>
       </c>
-      <c r="E30" t="str">
-        <f>_xlfn.CONCAT("'Mixed_Zebu@1'+(30/100)*'Mixed_Zebu@1'*(",G30,")")</f>
+      <c r="E40" t="str">
+        <f>_xlfn.CONCAT("'Mixed_Zebu@1'+(30/100)*'Mixed_Zebu@1'*(",G40,")")</f>
         <v>'Mixed_Zebu@1'+(30/100)*'Mixed_Zebu@1'*(1.35458882134414)</v>
       </c>
-      <c r="G30">
+      <c r="G40">
         <f>[1]FAO_2019_animal_trends!G40</f>
         <v>1.354588821344141</v>
       </c>
     </row>
-    <row r="31" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D31" t="s">
+    <row r="41" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
         <v>18</v>
       </c>
-      <c r="E31" t="str">
-        <f>_xlfn.CONCAT("'Mixed_Boran@1'+(30/100)*'Mixed_Boran@1'*(",G30,")")</f>
+      <c r="E41" t="str">
+        <f>_xlfn.CONCAT("'Mixed_Boran@1'+(30/100)*'Mixed_Boran@1'*(",G40,")")</f>
         <v>'Mixed_Boran@1'+(30/100)*'Mixed_Boran@1'*(1.35458882134414)</v>
       </c>
     </row>
-    <row r="33" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D33" t="s">
+    <row r="43" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
         <v>20</v>
       </c>
-      <c r="E33" t="str">
-        <f>_xlfn.CONCAT("'Dairy_density_total_adj_h_km2@1'+(30/100)*'Dairy_density_total_adj_h_km2@1'*(",G33,")")</f>
+      <c r="E43" t="str">
+        <f>_xlfn.CONCAT("'Dairy_density_total_adj_h_km2@1'+(30/100)*'Dairy_density_total_adj_h_km2@1'*(",G43,")")</f>
         <v>'Dairy_density_total_adj_h_km2@1'+(30/100)*'Dairy_density_total_adj_h_km2@1'*(1.35458882134414)</v>
       </c>
-      <c r="G33">
+      <c r="G43">
         <f>[1]FAO_2019_animal_trends!G40</f>
         <v>1.354588821344141</v>
       </c>
     </row>
-    <row r="35" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D35" t="s">
+    <row r="45" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
         <v>21</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D39" t="s">
+    <row r="49" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D40">
+    <row r="50" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D50">
         <v>2020</v>
       </c>
     </row>
-    <row r="41" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D41" t="s">
+    <row r="51" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
         <v>24</v>
       </c>
-      <c r="E41" t="str">
-        <f>_xlfn.CONCAT("365*(1/100)*('Beef_density_total_adj_h_km2@1'*(",I41,")+'Dairy_density_total_adj_h_km2@1'*(",I42,"))*(1-(",I43,"))*(",I44,")")</f>
+      <c r="E51" t="str">
+        <f>_xlfn.CONCAT("365*(1/100)*('Beef_density_total_adj_h_km2@1'*(",I51,")+'Dairy_density_total_adj_h_km2@1'*(",I52,"))*(1-(",I53,"))*(",I54,")")</f>
         <v>365*(1/100)*('Beef_density_total_adj_h_km2@1'*(167)+'Dairy_density_total_adj_h_km2@1'*(200))*(1-(0.02))*(0.025)</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H51" t="s">
         <v>25</v>
       </c>
-      <c r="I41">
+      <c r="I51">
         <v>167</v>
       </c>
     </row>
-    <row r="42" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H42" t="s">
+    <row r="52" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="H52" t="s">
         <v>26</v>
       </c>
-      <c r="I42">
+      <c r="I52">
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H43" t="s">
+    <row r="53" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="H53" t="s">
         <v>27</v>
       </c>
-      <c r="I43">
+      <c r="I53">
         <v>0.02</v>
       </c>
     </row>
-    <row r="44" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H44" t="s">
+    <row r="54" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="H54" t="s">
         <v>28</v>
       </c>
-      <c r="I44">
+      <c r="I54">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="45" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D45">
+    <row r="55" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D55">
         <v>2050</v>
       </c>
     </row>
-    <row r="46" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D46" t="s">
+    <row r="56" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
         <v>24</v>
       </c>
-      <c r="E46" t="str">
-        <f>_xlfn.CONCAT("365*(1/100)*('Beef_density_total_2050_adj_h_km2@1'*(",I41,")+'Dairy_total_2050@1'*(",I42,"))*(1-(",I43,"))*(",I44,")")</f>
+      <c r="E56" t="str">
+        <f>_xlfn.CONCAT("365*(1/100)*('Beef_density_total_2050_adj_h_km2@1'*(",I51,")+'Dairy_total_2050@1'*(",I52,"))*(1-(",I53,"))*(",I54,")")</f>
         <v>365*(1/100)*('Beef_density_total_2050_adj_h_km2@1'*(167)+'Dairy_total_2050@1'*(200))*(1-(0.02))*(0.025)</v>
       </c>
     </row>
-    <row r="51" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D51" s="3" t="s">
+    <row r="61" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D61" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D52" s="3" t="s">
+    <row r="62" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D62" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="E53" t="s">
+    <row r="63" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="E63" t="s">
         <v>60</v>
       </c>
-      <c r="I53" t="s">
+      <c r="I63" t="s">
         <v>59</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J63" t="s">
         <v>63</v>
       </c>
-      <c r="K53" t="s">
+      <c r="K63" t="s">
         <v>62</v>
       </c>
-      <c r="L53" t="s">
+      <c r="L63" t="s">
         <v>64</v>
       </c>
-      <c r="M53" t="s">
+      <c r="M63" t="s">
         <v>65</v>
       </c>
-      <c r="N53" t="s">
+      <c r="N63" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="4:14" ht="75" x14ac:dyDescent="0.25">
-      <c r="D54" t="s">
+    <row r="64" spans="4:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
         <v>68</v>
       </c>
-      <c r="E54" s="4" t="str">
-        <f>_xlfn.CONCAT("('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*((",I54,")*(",G54,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*((",J54,")*(",G54,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*((",K54,")*(",G54,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=6)*((",L54,")*(",G54,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*((",M54,")*(",G54,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*((",N54,")*(",G54,")+1)
+      <c r="E64" s="4" t="str">
+        <f>_xlfn.CONCAT("('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*((",I64,")*(",G64,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*((",J64,")*(",G64,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*((",K64,")*(",G64,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=6)*((",L64,")*(",G64,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*((",M64,")*(",G64,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*((",N64,")*(",G64,")+1)
 ")</f>
         <v xml:space="preserve">('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*((0.104166666666667)*(0.16667)+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*((0)*(0.16667)+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*((-0.0952380952380953)*(0.16667)+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=6)*((0.0212765957446808)*(0.16667)+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*((-0.0599999999999999)*(0.16667)+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*((-0.126315789473684)*(0.16667)+1)
 </v>
       </c>
-      <c r="F54" t="s">
+      <c r="F64" t="s">
         <v>69</v>
       </c>
-      <c r="G54">
+      <c r="G64">
         <v>0.16667000000000001</v>
       </c>
-      <c r="I54">
-        <f>I55-1</f>
+      <c r="I64">
+        <f>I65-1</f>
         <v>0.10416666666666674</v>
       </c>
-      <c r="J54">
-        <f t="shared" ref="J54:N54" si="0">J55-1</f>
+      <c r="J64">
+        <f t="shared" ref="J64:N64" si="0">J65-1</f>
         <v>0</v>
       </c>
-      <c r="K54">
+      <c r="K64">
         <f t="shared" si="0"/>
         <v>-9.5238095238095344E-2</v>
       </c>
-      <c r="L54">
+      <c r="L64">
         <f t="shared" si="0"/>
         <v>2.1276595744680771E-2</v>
       </c>
-      <c r="M54">
+      <c r="M64">
         <f t="shared" si="0"/>
         <v>-5.9999999999999942E-2</v>
       </c>
-      <c r="N54">
+      <c r="N64">
         <f t="shared" si="0"/>
         <v>-0.12631578947368416</v>
       </c>
     </row>
-    <row r="55" spans="4:14" ht="126" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D55" s="3" t="s">
+    <row r="65" spans="4:14" ht="126" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D65" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E55" s="4" t="str">
-        <f>_xlfn.CONCAT("('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*(",I55,") +('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*(",J55,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*(",K55,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=6)*(",L55,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(",M55,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*(",N55,") 
+      <c r="E65" s="4" t="str">
+        <f>_xlfn.CONCAT("('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*(",I65,") +('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*(",J65,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*(",K65,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=6)*(",L65,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(",M65,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*(",N65,") 
 ")</f>
         <v xml:space="preserve">('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*(1.10416666666667) +('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*(1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*(0.904761904761905)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=6)*(1.02127659574468)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(0.94)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*(0.873684210526316) 
 </v>
       </c>
-      <c r="H55" t="s">
+      <c r="H65" t="s">
         <v>67</v>
       </c>
-      <c r="I55">
+      <c r="I65">
         <f>26.5/24</f>
         <v>1.1041666666666667</v>
       </c>
-      <c r="J55">
+      <c r="J65">
         <v>1</v>
       </c>
-      <c r="K55">
+      <c r="K65">
         <f>3.8/4.2</f>
         <v>0.90476190476190466</v>
       </c>
-      <c r="L55">
+      <c r="L65">
         <f>4.8/4.7</f>
         <v>1.0212765957446808</v>
       </c>
-      <c r="M55">
+      <c r="M65">
         <f>2.35/2.5</f>
         <v>0.94000000000000006</v>
       </c>
-      <c r="N55">
+      <c r="N65">
         <f>8.3/9.5</f>
         <v>0.87368421052631584</v>
       </c>
     </row>
-    <row r="56" spans="4:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="D56" s="3" t="s">
+    <row r="66" spans="4:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="D66" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E56" s="4" t="str">
-        <f>_xlfn.CONCAT("('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*(",I56,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*(",J56,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*(",K56,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(",L56,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(",M56,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*(",N56,") ) 
+      <c r="E66" s="4" t="str">
+        <f>_xlfn.CONCAT("('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*(",I66,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*(",J66,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*(",K66,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(",L66,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(",M66,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*(",N66,") ) 
 ")</f>
         <v xml:space="preserve">('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*(1.175)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*(1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*(0.892857142857143)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(1.01063829787234)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(0.86)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*(0.863157894736842) ) 
 </v>
       </c>
-      <c r="H56" t="s">
+      <c r="H66" t="s">
         <v>61</v>
       </c>
-      <c r="I56">
+      <c r="I66">
         <f>28.2/24</f>
         <v>1.175</v>
       </c>
-      <c r="J56">
+      <c r="J66">
         <v>1</v>
       </c>
-      <c r="K56">
+      <c r="K66">
         <f>3.75/4.2</f>
         <v>0.89285714285714279</v>
       </c>
-      <c r="L56">
+      <c r="L66">
         <f>4.75/4.7</f>
         <v>1.0106382978723405</v>
       </c>
-      <c r="M56">
+      <c r="M66">
         <f>2.15/2.5</f>
         <v>0.86</v>
       </c>
-      <c r="N56">
+      <c r="N66">
         <f>8.2/9.5</f>
         <v>0.86315789473684201</v>
       </c>
     </row>
-    <row r="57" spans="4:14" ht="84" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D57" s="3"/>
-      <c r="E57" s="4"/>
-    </row>
-    <row r="61" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D61" s="3" t="s">
+    <row r="67" spans="4:14" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D67" s="3"/>
+      <c r="E67" s="4"/>
+    </row>
+    <row r="71" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D71" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D62" s="3"/>
-      <c r="E62" t="s">
+    <row r="72" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D72" s="3"/>
+      <c r="E72" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="63" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D63" s="3">
+    <row r="73" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D73" s="3">
         <v>2020</v>
       </c>
     </row>
-    <row r="64" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D64" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F64" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="65" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D65" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F65" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="66" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D66" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F66" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="67" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D67" s="3"/>
-    </row>
-    <row r="68" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D68" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="69" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D69" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="70" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D70" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F70" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="71" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D71" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F71" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="72" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D72" s="3"/>
-    </row>
-    <row r="73" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D73" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="74" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D74" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E74" s="9" t="s">
-        <v>80</v>
+      <c r="E74" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="F74" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="75" spans="4:9" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="75" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D75" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E75" s="10" t="s">
-        <v>81</v>
+      <c r="E75" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="F75" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="76" spans="4:9" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="76" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D76" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E76" s="10" t="s">
-        <v>82</v>
+      <c r="E76" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="F76" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="77" spans="4:9" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="77" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D77" s="3"/>
     </row>
-    <row r="79" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D78" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="79" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D79" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E79" t="str">
-        <f>_xlfn.CONCAT("'MODIS_2020_ALL_final@1'*(((2020_LC_is_grassland@1=1)*(",I84,"))+((2020_LC_is_cropland@1=1)(",I85,"))+((2020_LC_is_shrubland@1=1)*(",I86,")))*(",I79,")*(",I80,")*(",I81,")")</f>
-        <v>'MODIS_2020_ALL_final@1'*(((2020_LC_is_grassland@1=1)*(1))+((2020_LC_is_cropland@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.365)</v>
-      </c>
-      <c r="H79" t="s">
-        <v>35</v>
-      </c>
-      <c r="I79">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="80" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D80" s="3"/>
-      <c r="H80" t="s">
-        <v>36</v>
-      </c>
-      <c r="I80">
-        <v>0.44</v>
+        <v>54</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="80" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D80" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F80" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="81" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D81" s="3"/>
-      <c r="H81" t="s">
-        <v>89</v>
-      </c>
-      <c r="I81" s="12">
-        <v>0.36499999999999999</v>
+      <c r="D81" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F81" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="82" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D82" s="3"/>
-      <c r="H82" t="s">
-        <v>90</v>
-      </c>
-      <c r="I82" s="12">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="83" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D83" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E83" t="str">
-        <f>_xlfn.CONCAT("'MODIS_2020_ALL_final@1'*(((2020_LC_is_cropland@1=1)*(",I92,")))*(",I88,")*(",I89,")*(",I90,")")</f>
-        <v>'MODIS_2020_ALL_final@1'*(((2020_LC_is_cropland@1=1)*(0.4)))*(0.4)*(0.5)*(0.7)</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D84" s="3"/>
-      <c r="H84" t="s">
-        <v>38</v>
-      </c>
-      <c r="I84" s="5">
-        <v>1</v>
+      <c r="D84" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F84" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="85" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D85" s="3"/>
-      <c r="H85" t="s">
-        <v>39</v>
-      </c>
-      <c r="I85" s="5">
-        <v>0.34</v>
+      <c r="D85" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F85" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="86" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D86" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F86" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="87" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D87" s="3"/>
+    </row>
+    <row r="89" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D89" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E89" t="str">
+        <f>_xlfn.CONCAT("'MODIS_2020_ALL_final@1'*(((2020_LC_is_grassland@1=1)*(",I94,"))+((2020_LC_is_cropland@1=1)(",I95,"))+((2020_LC_is_shrubland@1=1)*(",I96,")))*(",I89,")*(",I90,")*(",I91,")")</f>
+        <v>'MODIS_2020_ALL_final@1'*(((2020_LC_is_grassland@1=1)*(1))+((2020_LC_is_cropland@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.4015)</v>
+      </c>
+      <c r="H89" t="s">
+        <v>35</v>
+      </c>
+      <c r="I89">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="90" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D90" s="3"/>
+      <c r="H90" t="s">
+        <v>36</v>
+      </c>
+      <c r="I90">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="91" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D91" s="3"/>
+      <c r="H91" t="s">
+        <v>89</v>
+      </c>
+      <c r="I91" s="12">
+        <f>0.365*1.1</f>
+        <v>0.40150000000000002</v>
+      </c>
+    </row>
+    <row r="92" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D92" s="3"/>
+      <c r="H92" t="s">
+        <v>90</v>
+      </c>
+      <c r="I92" s="12">
+        <f>0.4*1.15</f>
+        <v>0.45999999999999996</v>
+      </c>
+    </row>
+    <row r="93" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D93" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E93" t="str">
+        <f>_xlfn.CONCAT("'MODIS_2020_ALL_final@1'*(((2020_LC_is_cropland@1=1)*(",I102,")))*(",I98,")*(",I99,")*(",I100,")")</f>
+        <v>'MODIS_2020_ALL_final@1'*(((2020_LC_is_cropland@1=1)*(0.4)))*(0.4)*(0.5)*(0.7)</v>
+      </c>
+    </row>
+    <row r="94" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D94" s="3"/>
+      <c r="H94" t="s">
+        <v>38</v>
+      </c>
+      <c r="I94" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D95" s="3"/>
+      <c r="H95" t="s">
+        <v>39</v>
+      </c>
+      <c r="I95" s="5">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="96" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D96" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E96" t="s">
         <v>41</v>
       </c>
-      <c r="H86" t="s">
+      <c r="H96" t="s">
         <v>42</v>
       </c>
-      <c r="I86" s="5">
+      <c r="I96" s="5">
         <v>0.4</v>
       </c>
     </row>
-    <row r="87" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H87" t="s">
+    <row r="97" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H97" t="s">
         <v>58</v>
       </c>
-      <c r="I87" s="5">
+      <c r="I97" s="5">
         <v>0.85</v>
       </c>
     </row>
-    <row r="88" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D88" s="3" t="s">
+    <row r="98" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D98" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H88" s="6" t="s">
+      <c r="H98" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I88" s="5">
+      <c r="I98" s="5">
         <v>0.4</v>
       </c>
     </row>
-    <row r="89" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="H89" s="6" t="s">
+    <row r="99" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="H99" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I89" s="5">
+      <c r="I99" s="5">
         <v>0.5</v>
       </c>
     </row>
-    <row r="90" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D90" t="s">
+    <row r="100" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
         <v>46</v>
       </c>
-      <c r="H90" s="6" t="s">
+      <c r="H100" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I90" s="11">
+      <c r="I100" s="11">
         <v>0.7</v>
       </c>
     </row>
-    <row r="91" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D91" t="s">
+    <row r="101" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
         <v>48</v>
       </c>
-      <c r="E91" t="str">
-        <f>_xlfn.CONCAT("'MODIS_NPP_2050_R4@1'*(((2020_LC_is_grassland@1=1)*(",I84,"))+((2020_LC_is_cropland@1=1)(",I85,"))+((2020_LC_is_shrubland@1=1)*(",I86,")))*(",I79,")*(",I80,")*(",I81,")")</f>
-        <v>'MODIS_NPP_2050_R4@1'*(((2020_LC_is_grassland@1=1)*(1))+((2020_LC_is_cropland@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.365)</v>
-      </c>
-    </row>
-    <row r="92" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D92" t="s">
+      <c r="E101" t="str">
+        <f>_xlfn.CONCAT("'MODIS_NPP_2050_R4@1'*(((2020_LC_is_grassland@1=1)*(",I94,"))+((2020_LC_is_cropland@1=1)(",I95,"))+((2020_LC_is_shrubland@1=1)*(",I96,")))*(",I89,")*(",I90,")*(",I91,")")</f>
+        <v>'MODIS_NPP_2050_R4@1'*(((2020_LC_is_grassland@1=1)*(1))+((2020_LC_is_cropland@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.4015)</v>
+      </c>
+    </row>
+    <row r="102" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D102" t="s">
         <v>49</v>
       </c>
-      <c r="E92" t="str">
-        <f>_xlfn.CONCAT("'MODIS_NPP_2050_R8@1'*(((2020_LC_is_grassland)*(",I84,"))+((E75@1=1)(",I85,"))+((2020_LC_is_shrubland@1=1)*(",I86,")))*(",I79,")*(",I80,")*(",I81,")")</f>
-        <v>'MODIS_NPP_2050_R8@1'*(((2020_LC_is_grassland)*(1))+((E75@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.365)</v>
-      </c>
-      <c r="H92" t="s">
+      <c r="E102" t="str">
+        <f>_xlfn.CONCAT("'MODIS_NPP_2050_R8@1'*(((2020_LC_is_grassland)*(",I94,"))+((E75@1=1)(",I95,"))+((2020_LC_is_shrubland@1=1)*(",I96,")))*(",I89,")*(",I90,")*(",I91,")")</f>
+        <v>'MODIS_NPP_2050_R8@1'*(((2020_LC_is_grassland)*(1))+((E75@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.4015)</v>
+      </c>
+      <c r="H102" t="s">
         <v>50</v>
       </c>
-      <c r="I92" s="5">
+      <c r="I102" s="5">
         <v>0.4</v>
       </c>
     </row>
-    <row r="94" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D94" t="s">
+    <row r="104" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
         <v>51</v>
       </c>
-      <c r="I94" s="5"/>
-    </row>
-    <row r="95" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D95" t="s">
+      <c r="I104" s="5"/>
+    </row>
+    <row r="105" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
         <v>48</v>
       </c>
-      <c r="E95" t="str">
-        <f>_xlfn.CONCAT("'MODIS_NPP_2050_R4@1'*(((2020_LC_is_cropland@1=1)*(",I92,")))*(",I88,")*(",I89,")*(",I90,")")</f>
+      <c r="E105" t="str">
+        <f>_xlfn.CONCAT("'MODIS_NPP_2050_R4@1'*(((2020_LC_is_cropland@1=1)*(",I102,")))*(",I98,")*(",I99,")*(",I100,")")</f>
         <v>'MODIS_NPP_2050_R4@1'*(((2020_LC_is_cropland@1=1)*(0.4)))*(0.4)*(0.5)*(0.7)</v>
       </c>
     </row>
-    <row r="96" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D96" t="s">
+    <row r="106" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D106" t="s">
         <v>49</v>
       </c>
-      <c r="E96" t="str">
-        <f>_xlfn.CONCAT("'MODIS_NPP_2050_R8@1'*(((2020_LC_is_cropland@1=1)*(",I92,")))*(",I88,")*(",I89,")*(",I90,")")</f>
+      <c r="E106" t="str">
+        <f>_xlfn.CONCAT("'MODIS_NPP_2050_R8@1'*(((2020_LC_is_cropland@1=1)*(",I102,")))*(",I98,")*(",I99,")*(",I100,")")</f>
         <v>'MODIS_NPP_2050_R8@1'*(((2020_LC_is_cropland@1=1)*(0.4)))*(0.4)*(0.5)*(0.7)</v>
       </c>
     </row>
-    <row r="98" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D98" s="3" t="s">
+    <row r="108" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D108" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E108" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="99" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D99" t="s">
+    <row r="109" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D109" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="100" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D100" t="s">
+    <row r="110" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
         <v>53</v>
       </c>
     </row>

--- a/Raster.logic.xlsx
+++ b/Raster.logic.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3E69B8-2678-4849-8F98-00CDF83450FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E8C4D828-59A7-4D6B-8FA1-BE0758A76F31}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{E8C4D828-59A7-4D6B-8FA1-BE0758A76F31}"/>
   </bookViews>
   <sheets>
     <sheet name="Raster_logic" sheetId="1" r:id="rId1"/>
@@ -460,6 +460,9 @@
       <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="35">
+          <cell r="F35">
+            <v>0.53615960099750615</v>
+          </cell>
           <cell r="G35">
             <v>0.38312009613345605</v>
           </cell>

--- a/Raster.logic.xlsx
+++ b/Raster.logic.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\KE.beef.spatial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3E69B8-2678-4849-8F98-00CDF83450FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22144BC-EAD6-4C39-830C-AE5F31B9DCB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{E8C4D828-59A7-4D6B-8FA1-BE0758A76F31}"/>
   </bookViews>
@@ -17,6 +17,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="99">
   <si>
     <t>Finisher Boran</t>
   </si>
@@ -59,9 +60,6 @@
     <t>Cowcalf Boran</t>
   </si>
   <si>
-    <t>(",H7,")</t>
-  </si>
-  <si>
     <t>Cowcalf Exotic</t>
   </si>
   <si>
@@ -329,13 +327,19 @@
     <t>BC</t>
   </si>
   <si>
-    <t>(1/1000)*(1/100)*365*0.02*("Beef_density_total_adj_h_km2@1"*196.1 + "Sheep_density_total_h_km2@1" *30 + "Dairy_density_total_adj_h_km2@1"*201 )*( 1-0.065)</t>
-  </si>
-  <si>
-    <t>(1/1000)*(1/100)*365*0.02*("Beef_density_total_adj_h_km2@1"*194.3 + "Sheep_density_total_h_km2@1" *30 + "Dairy_density_total_adj_h_km2@1"*201 )*( 1-0.065)</t>
-  </si>
-  <si>
-    <t>(1/1000)*(1/100)*365*0.02*("Beef_density_total_adj_h_km2@1"*198.1 + "Sheep_density_total_h_km2@1" *30 + "Dairy_density_total_adj_h_km2@1"*201 )*( 1-0.065)</t>
+    <t>Mean weight - Cattle - WC</t>
+  </si>
+  <si>
+    <t>Mean weight - Cattle - BL</t>
+  </si>
+  <si>
+    <t>Mean weight - Cattle - BC</t>
+  </si>
+  <si>
+    <t>Mean weight - Sheep - BC</t>
+  </si>
+  <si>
+    <t>Mean weight - Dairy - BC</t>
   </si>
 </sst>
 </file>
@@ -488,6 +492,77 @@
           </cell>
         </row>
       </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Validate_2020"/>
+      <sheetName val="Herd_decision_tree"/>
+      <sheetName val="Projections"/>
+      <sheetName val="ZS_Summary"/>
+      <sheetName val="NPP"/>
+      <sheetName val="Carrying_Capacity"/>
+      <sheetName val="CC_to_Rumen8.io"/>
+      <sheetName val="Beef_population_to_GIS"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="I2">
+            <v>3.5000000000000003E-2</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="I3">
+            <v>0.68</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>0.76913039999999999</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="I8">
+            <v>0.5848000000000001</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="I9">
+            <v>0.15670000000000001</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="I11">
+            <v>0.1244</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="I12">
+            <v>7.0000000000000007E-2</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="I13">
+            <v>0.08</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -815,6 +890,7 @@
   <cols>
     <col min="4" max="4" width="28.42578125" customWidth="1"/>
     <col min="5" max="5" width="141.85546875" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -824,13 +900,14 @@
       </c>
       <c r="E2" t="str">
         <f>_xlfn.CONCAT("('Beef_density_comm_adj_h_km2@1' + 'Beef_density_subs_adj_h_km2@1' )* (",H2,") * ((",H3,"))")</f>
-        <v>('Beef_density_comm_adj_h_km2@1' + 'Beef_density_subs_adj_h_km2@1' )* (0.002) * ((0.68))</v>
+        <v>('Beef_density_comm_adj_h_km2@1' + 'Beef_density_subs_adj_h_km2@1' )* (0.035) * ((0.68))</v>
       </c>
       <c r="G2" t="s">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>2E-3</v>
+        <f>[2]Herd_decision_tree!$I$2</f>
+        <v>3.5000000000000003E-2</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
@@ -839,12 +916,13 @@
       </c>
       <c r="E3" t="str">
         <f>_xlfn.CONCAT("('Beef_density_comm_adj_h_km2@1' + 'Beef_density_subs_adj_h_km2@1' )* (",H2,")* (1-(",H3,"))")</f>
-        <v>('Beef_density_comm_adj_h_km2@1' + 'Beef_density_subs_adj_h_km2@1' )* (0.002)* (1-(0.68))</v>
+        <v>('Beef_density_comm_adj_h_km2@1' + 'Beef_density_subs_adj_h_km2@1' )* (0.035)* (1-(0.68))</v>
       </c>
       <c r="G3" t="s">
         <v>3</v>
       </c>
       <c r="H3">
+        <f>[2]Herd_decision_tree!$I$3</f>
         <v>0.68</v>
       </c>
     </row>
@@ -858,155 +936,189 @@
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="1"/>
+      <c r="D5" t="s">
         <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
       </c>
       <c r="E5" t="str">
         <f>_xlfn.CONCAT("(('Beef_density_comm_adj_h_km2@1') - 'Finisher_Boran@1' - 'Finisher_Exotic@1') * (1-",H3,")")</f>
         <v>(('Beef_density_comm_adj_h_km2@1') - 'Finisher_Boran@1' - 'Finisher_Exotic@1') * (1-0.68)</v>
       </c>
       <c r="G5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" s="2">
-        <f>0.7391304+0.085-I5</f>
-        <v>0.82413039999999993</v>
+        <f>[2]Herd_decision_tree!$I7</f>
+        <v>0.76913039999999999</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H6" s="2">
-        <f>0.5348+0.15-I6</f>
-        <v>0.68480000000000008</v>
+        <f>[2]Herd_decision_tree!$I8</f>
+        <v>0.5848000000000001</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" t="str">
         <f>_xlfn.CONCAT("('Beef_density_subs_adj_h_km2@1')*(('Hybrid_AEZs@1'=1)*((",H5,"))*(1-(",H9,"))+('Hybrid_AEZs@1'=2)*((",H6,"))*(1-(",H9,")))")</f>
-        <v>('Beef_density_subs_adj_h_km2@1')*(('Hybrid_AEZs@1'=1)*((0.8241304))*(1-(0.1244))+('Hybrid_AEZs@1'=2)*((0.6848))*(1-(0.1244)))</v>
+        <v>('Beef_density_subs_adj_h_km2@1')*(('Hybrid_AEZs@1'=1)*((0.7691304))*(1-(0.1244))+('Hybrid_AEZs@1'=2)*((0.5848))*(1-(0.1244)))</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <f>0.0567</f>
-        <v>5.67E-2</v>
+        <v>9</v>
+      </c>
+      <c r="H7" s="2">
+        <f>[2]Herd_decision_tree!$I9</f>
+        <v>0.15670000000000001</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" t="str">
         <f>_xlfn.CONCAT("('Beef_density_subs_adj_h_km2@1')*(('Hybrid_AEZs@1'=1)*((",H5,"))*((",H9,"))+('Hybrid_AEZs@1'=2)*((",H6,"))*((",H9,")))")</f>
-        <v>('Beef_density_subs_adj_h_km2@1')*(('Hybrid_AEZs@1'=1)*((0.8241304))*((0.1244))+('Hybrid_AEZs@1'=2)*((0.6848))*((0.1244)))</v>
+        <v>('Beef_density_subs_adj_h_km2@1')*(('Hybrid_AEZs@1'=1)*((0.7691304))*((0.1244))+('Hybrid_AEZs@1'=2)*((0.5848))*((0.1244)))</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H9">
-        <f>(0.1244)</f>
+        <f>[2]Herd_decision_tree!$I11</f>
         <v>0.1244</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" t="str">
         <f>_xlfn.CONCAT("('Beef_density_subs_adj_h_km2@1')*(('Hybrid_AEZs@1'=2)*(1-(",H6,"))*(1-(",H10,"))+('Hybrid_AEZs@1'=3 OR 'Hybrid_AEZs@1'=4 OR 'Hybrid_AEZs@1'=5)*(1-(",H6,"))*(1-(",H10,")))")</f>
-        <v>('Beef_density_subs_adj_h_km2@1')*(('Hybrid_AEZs@1'=2)*(1-(0.6848))*(1-(0.07))+('Hybrid_AEZs@1'=3 OR 'Hybrid_AEZs@1'=4 OR 'Hybrid_AEZs@1'=5)*(1-(0.6848))*(1-(0.07)))</v>
+        <v>('Beef_density_subs_adj_h_km2@1')*(('Hybrid_AEZs@1'=2)*(1-(0.5848))*(1-(0.07))+('Hybrid_AEZs@1'=3 OR 'Hybrid_AEZs@1'=4 OR 'Hybrid_AEZs@1'=5)*(1-(0.5848))*(1-(0.07)))</v>
       </c>
       <c r="G10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H10">
-        <f>(0.07)</f>
+        <f>[2]Herd_decision_tree!$I12</f>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11" t="str">
         <f>_xlfn.CONCAT("('Beef_density_subs_adj_h_km2@1')*(('Hybrid_AEZs@1'=2)*(1-(",H6,"))*((",H10,"))+('Hybrid_AEZs@1'=3 OR 'Hybrid_AEZs@1'=4 OR 'Hybrid_AEZs@1'=5)*(1-(",H6,"))*((",H10,")))")</f>
-        <v>('Beef_density_subs_adj_h_km2@1')*(('Hybrid_AEZs@1'=2)*(1-(0.6848))*((0.07))+('Hybrid_AEZs@1'=3 OR 'Hybrid_AEZs@1'=4 OR 'Hybrid_AEZs@1'=5)*(1-(0.6848))*((0.07)))</v>
+        <v>('Beef_density_subs_adj_h_km2@1')*(('Hybrid_AEZs@1'=2)*(1-(0.5848))*((0.07))+('Hybrid_AEZs@1'=3 OR 'Hybrid_AEZs@1'=4 OR 'Hybrid_AEZs@1'=5)*(1-(0.5848))*((0.07)))</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H11">
-        <f>(0.08)</f>
+        <f>[2]Herd_decision_tree!$I13</f>
         <v>0.08</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E13" t="str">
         <f>_xlfn.CONCAT("('Beef_density_subs_adj_h_km2@1')*('Hybrid_AEZs@1'=3 OR 'Hybrid_AEZs@1'=4 OR 'Hybrid_AEZs@1'=5)*((",H7,"))*(1-(",H11,"))")</f>
-        <v>('Beef_density_subs_adj_h_km2@1')*('Hybrid_AEZs@1'=3 OR 'Hybrid_AEZs@1'=4 OR 'Hybrid_AEZs@1'=5)*((0.0567))*(1-(0.08))</v>
+        <v>('Beef_density_subs_adj_h_km2@1')*('Hybrid_AEZs@1'=3 OR 'Hybrid_AEZs@1'=4 OR 'Hybrid_AEZs@1'=5)*((0.1567))*(1-(0.08))</v>
+      </c>
+      <c r="G13" t="s">
+        <v>94</v>
+      </c>
+      <c r="H13">
+        <v>196.1</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" t="str">
         <f>_xlfn.CONCAT("('Beef_density_subs_adj_h_km2@1')*('Hybrid_AEZs@1'=3 OR 'Hybrid_AEZs@1'=4 OR 'Hybrid_AEZs@1'=5)*((",H7,"))*((",H11,"))")</f>
-        <v>('Beef_density_subs_adj_h_km2@1')*('Hybrid_AEZs@1'=3 OR 'Hybrid_AEZs@1'=4 OR 'Hybrid_AEZs@1'=5)*((0.0567))*((0.08))</v>
-      </c>
-    </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
+        <v>('Beef_density_subs_adj_h_km2@1')*('Hybrid_AEZs@1'=3 OR 'Hybrid_AEZs@1'=4 OR 'Hybrid_AEZs@1'=5)*((0.1567))*((0.08))</v>
+      </c>
+      <c r="G14" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14">
+        <v>196.1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15">
+        <v>196.1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H16">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="19" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D20" t="s">
+      <c r="E20" t="str">
+        <f>_xlfn.CONCAT("(1/1000)*(1/100)*365*0.02*('Beef_density_total_adj_h_km2@1'*",H13," + 'Sheep_density_total_h_km2@1' '*",H16,"+ 'Dairy_density_total_adj_h_km2@1''*",H17," )*( 1-0.065)")</f>
+        <v>(1/1000)*(1/100)*365*0.02*('Beef_density_total_adj_h_km2@1'*196.1 + 'Sheep_density_total_h_km2@1' '*30+ 'Dairy_density_total_adj_h_km2@1''*201 )*( 1-0.065)</v>
+      </c>
+    </row>
+    <row r="21" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
         <v>92</v>
       </c>
-      <c r="E20" t="s">
-        <v>95</v>
-      </c>
-      <c r="F20" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D21" t="s">
+      <c r="E21" t="str">
+        <f>_xlfn.CONCAT("(1/1000)*(1/100)*365*0.02*('Beef_density_total_adj_h_km2@1'*",H14," + 'Sheep_density_total_h_km2@1' '*",H16,"+ 'Dairy_density_total_adj_h_km2@1''*",H17," )*( 1-0.065)")</f>
+        <v>(1/1000)*(1/100)*365*0.02*('Beef_density_total_adj_h_km2@1'*196.1 + 'Sheep_density_total_h_km2@1' '*30+ 'Dairy_density_total_adj_h_km2@1''*201 )*( 1-0.065)</v>
+      </c>
+    </row>
+    <row r="22" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
         <v>93</v>
       </c>
-      <c r="F21" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="E22" t="str">
+        <f>_xlfn.CONCAT("(1/1000)*(1/100)*365*0.02*('Beef_density_total_adj_h_km2@1'*",H15," + 'Sheep_density_total_h_km2@1' '*",H16,"+ 'Dairy_density_total_adj_h_km2@1''*",H17," )*( 1-0.065)")</f>
+        <v>(1/1000)*(1/100)*365*0.02*('Beef_density_total_adj_h_km2@1'*196.1 + 'Sheep_density_total_h_km2@1' '*30+ 'Dairy_density_total_adj_h_km2@1''*201 )*( 1-0.065)</v>
+      </c>
+    </row>
+    <row r="27" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D27" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="4:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D29" t="s">
         <v>0</v>
       </c>
@@ -1019,7 +1131,7 @@
         <v>86.466565349544069</v>
       </c>
     </row>
-    <row r="30" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D30" t="s">
         <v>2</v>
       </c>
@@ -1028,7 +1140,7 @@
         <v>'Finisher_Exotic@1'+(30/100)*'Finisher_Exotic@1'*(86.4665653495441)</v>
       </c>
     </row>
-    <row r="31" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D31" t="s">
         <v>4</v>
       </c>
@@ -1041,9 +1153,9 @@
         <v>1.0372340425531916</v>
       </c>
     </row>
-    <row r="32" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" t="str">
         <f>_xlfn.CONCAT("'Cowcalf_Exotic@1'+(30/100)*'Cowcalf_Exotic@1'*(",G31,")")</f>
@@ -1052,7 +1164,7 @@
     </row>
     <row r="34" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E34" t="str">
         <f>_xlfn.CONCAT("'Pastoral_Zebu@1'+(30/100)*'Pastoral_Zebu@1'*(",G34,")")</f>
@@ -1065,7 +1177,7 @@
     </row>
     <row r="35" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E35" t="str">
         <f>_xlfn.CONCAT("'Pastoral_Boran@1'+(30/100)*'Pastoral_Boran@1'*(",G34,")")</f>
@@ -1074,7 +1186,7 @@
     </row>
     <row r="37" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E37" t="str">
         <f>_xlfn.CONCAT("'Agpastoral_Zebu@1'+(30/100)*'Agpastoral_Zebu@1'*(",G37,")")</f>
@@ -1087,7 +1199,7 @@
     </row>
     <row r="38" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E38" t="str">
         <f>_xlfn.CONCAT("'Agpastoral_Boran@1'+(30/100)*'Agpastoral_Boran@1'*(",G37,")")</f>
@@ -1096,7 +1208,7 @@
     </row>
     <row r="40" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E40" t="str">
         <f>_xlfn.CONCAT("'Mixed_Zebu@1'+(30/100)*'Mixed_Zebu@1'*(",G40,")")</f>
@@ -1109,7 +1221,7 @@
     </row>
     <row r="41" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E41" t="str">
         <f>_xlfn.CONCAT("'Mixed_Boran@1'+(30/100)*'Mixed_Boran@1'*(",G40,")")</f>
@@ -1118,7 +1230,7 @@
     </row>
     <row r="43" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E43" t="str">
         <f>_xlfn.CONCAT("'Dairy_density_total_adj_h_km2@1'+(30/100)*'Dairy_density_total_adj_h_km2@1'*(",G43,")")</f>
@@ -1131,15 +1243,15 @@
     </row>
     <row r="45" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D45" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="49" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="4:14" x14ac:dyDescent="0.25">
@@ -1149,14 +1261,14 @@
     </row>
     <row r="51" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E51" t="str">
         <f>_xlfn.CONCAT("365*(1/100)*('Beef_density_total_adj_h_km2@1'*(",I51,")+'Dairy_density_total_adj_h_km2@1'*(",I52,"))*(1-(",I53,"))*(",I54,")")</f>
         <v>365*(1/100)*('Beef_density_total_adj_h_km2@1'*(167)+'Dairy_density_total_adj_h_km2@1'*(200))*(1-(0.02))*(0.025)</v>
       </c>
       <c r="H51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I51">
         <v>167</v>
@@ -1164,7 +1276,7 @@
     </row>
     <row r="52" spans="4:14" x14ac:dyDescent="0.25">
       <c r="H52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I52">
         <v>200</v>
@@ -1172,7 +1284,7 @@
     </row>
     <row r="53" spans="4:14" x14ac:dyDescent="0.25">
       <c r="H53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I53">
         <v>0.02</v>
@@ -1180,7 +1292,7 @@
     </row>
     <row r="54" spans="4:14" x14ac:dyDescent="0.25">
       <c r="H54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I54">
         <v>2.5000000000000001E-2</v>
@@ -1193,7 +1305,7 @@
     </row>
     <row r="56" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E56" t="str">
         <f>_xlfn.CONCAT("365*(1/100)*('Beef_density_total_2050_adj_h_km2@1'*(",I51,")+'Dairy_total_2050@1'*(",I52,"))*(1-(",I53,"))*(",I54,")")</f>
@@ -1202,40 +1314,40 @@
     </row>
     <row r="61" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D61" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D62" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="4:14" x14ac:dyDescent="0.25">
       <c r="E63" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I63" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J63" t="s">
+        <v>62</v>
+      </c>
+      <c r="K63" t="s">
+        <v>61</v>
+      </c>
+      <c r="L63" t="s">
         <v>63</v>
       </c>
-      <c r="K63" t="s">
-        <v>62</v>
-      </c>
-      <c r="L63" t="s">
+      <c r="M63" t="s">
         <v>64</v>
       </c>
-      <c r="M63" t="s">
+      <c r="N63" t="s">
         <v>65</v>
-      </c>
-      <c r="N63" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="64" spans="4:14" ht="75" x14ac:dyDescent="0.25">
       <c r="D64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E64" s="4" t="str">
         <f>_xlfn.CONCAT("('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*((",I64,")*(",G64,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*((",J64,")*(",G64,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*((",K64,")*(",G64,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=6)*((",L64,")*(",G64,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*((",M64,")*(",G64,")+1)+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*((",N64,")*(",G64,")+1)
@@ -1244,7 +1356,7 @@
 </v>
       </c>
       <c r="F64" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G64">
         <v>0.16667000000000001</v>
@@ -1276,7 +1388,7 @@
     </row>
     <row r="65" spans="4:14" ht="126" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E65" s="4" t="str">
         <f>_xlfn.CONCAT("('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*(",I65,") +('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*(",J65,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*(",K65,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=6)*(",L65,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(",M65,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*(",N65,") 
@@ -1285,7 +1397,7 @@
 </v>
       </c>
       <c r="H65" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I65">
         <f>26.5/24</f>
@@ -1313,7 +1425,7 @@
     </row>
     <row r="66" spans="4:14" ht="60" x14ac:dyDescent="0.25">
       <c r="D66" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E66" s="4" t="str">
         <f>_xlfn.CONCAT("('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=2)*(",I66,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=3)*(",J66,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=4)*(",K66,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(",L66,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=7)*(",M66,")+('MODIS_NPP_RAST_2014_LR@1')*('clipped_LPS@1'=8)*(",N66,") ) 
@@ -1322,7 +1434,7 @@
 </v>
       </c>
       <c r="H66" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I66">
         <f>28.2/24</f>
@@ -1354,13 +1466,13 @@
     </row>
     <row r="71" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D71" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D72" s="3"/>
       <c r="E72" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="4:14" x14ac:dyDescent="0.25">
@@ -1370,35 +1482,35 @@
     </row>
     <row r="74" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D74" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F74" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="75" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D75" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F75" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D76" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F76" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="4:14" x14ac:dyDescent="0.25">
@@ -1406,37 +1518,37 @@
     </row>
     <row r="78" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D78" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D79" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="80" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D80" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F80" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D81" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F81" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82" spans="4:9" x14ac:dyDescent="0.25">
@@ -1444,40 +1556,40 @@
     </row>
     <row r="83" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D83" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D84" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F84" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D85" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F85" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="86" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D86" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F86" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="87" spans="4:9" x14ac:dyDescent="0.25">
@@ -1485,14 +1597,14 @@
     </row>
     <row r="89" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D89" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E89" t="str">
         <f>_xlfn.CONCAT("'MODIS_2020_ALL_final@1'*(((2020_LC_is_grassland@1=1)*(",I94,"))+((2020_LC_is_cropland@1=1)(",I95,"))+((2020_LC_is_shrubland@1=1)*(",I96,")))*(",I89,")*(",I90,")*(",I91,")")</f>
         <v>'MODIS_2020_ALL_final@1'*(((2020_LC_is_grassland@1=1)*(1))+((2020_LC_is_cropland@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.4015)</v>
       </c>
       <c r="H89" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I89">
         <v>0.5</v>
@@ -1501,7 +1613,7 @@
     <row r="90" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D90" s="3"/>
       <c r="H90" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I90">
         <v>0.44</v>
@@ -1510,7 +1622,7 @@
     <row r="91" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D91" s="3"/>
       <c r="H91" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I91" s="12">
         <f>0.365*1.1</f>
@@ -1520,7 +1632,7 @@
     <row r="92" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D92" s="3"/>
       <c r="H92" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I92" s="12">
         <f>0.4*1.15</f>
@@ -1529,7 +1641,7 @@
     </row>
     <row r="93" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D93" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E93" t="str">
         <f>_xlfn.CONCAT("'MODIS_2020_ALL_final@1'*(((2020_LC_is_cropland@1=1)*(",I102,")))*(",I98,")*(",I99,")*(",I100,")")</f>
@@ -1539,7 +1651,7 @@
     <row r="94" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D94" s="3"/>
       <c r="H94" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I94" s="5">
         <v>1</v>
@@ -1548,7 +1660,7 @@
     <row r="95" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D95" s="3"/>
       <c r="H95" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I95" s="5">
         <v>0.34</v>
@@ -1556,13 +1668,13 @@
     </row>
     <row r="96" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D96" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E96" t="s">
         <v>40</v>
       </c>
-      <c r="E96" t="s">
+      <c r="H96" t="s">
         <v>41</v>
-      </c>
-      <c r="H96" t="s">
-        <v>42</v>
       </c>
       <c r="I96" s="5">
         <v>0.4</v>
@@ -1570,7 +1682,7 @@
     </row>
     <row r="97" spans="4:9" x14ac:dyDescent="0.25">
       <c r="H97" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I97" s="5">
         <v>0.85</v>
@@ -1578,10 +1690,10 @@
     </row>
     <row r="98" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D98" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>44</v>
       </c>
       <c r="I98" s="5">
         <v>0.4</v>
@@ -1589,7 +1701,7 @@
     </row>
     <row r="99" spans="4:9" x14ac:dyDescent="0.25">
       <c r="H99" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I99" s="5">
         <v>0.5</v>
@@ -1597,10 +1709,10 @@
     </row>
     <row r="100" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D100" t="s">
+        <v>45</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="I100" s="11">
         <v>0.7</v>
@@ -1608,7 +1720,7 @@
     </row>
     <row r="101" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D101" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E101" t="str">
         <f>_xlfn.CONCAT("'MODIS_NPP_2050_R4@1'*(((2020_LC_is_grassland@1=1)*(",I94,"))+((2020_LC_is_cropland@1=1)(",I95,"))+((2020_LC_is_shrubland@1=1)*(",I96,")))*(",I89,")*(",I90,")*(",I91,")")</f>
@@ -1617,14 +1729,14 @@
     </row>
     <row r="102" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D102" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E102" t="str">
         <f>_xlfn.CONCAT("'MODIS_NPP_2050_R8@1'*(((2020_LC_is_grassland)*(",I94,"))+((E75@1=1)(",I95,"))+((2020_LC_is_shrubland@1=1)*(",I96,")))*(",I89,")*(",I90,")*(",I91,")")</f>
         <v>'MODIS_NPP_2050_R8@1'*(((2020_LC_is_grassland)*(1))+((E75@1=1)(0.34))+((2020_LC_is_shrubland@1=1)*(0.4)))*(0.5)*(0.44)*(0.4015)</v>
       </c>
       <c r="H102" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I102" s="5">
         <v>0.4</v>
@@ -1632,13 +1744,13 @@
     </row>
     <row r="104" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D104" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I104" s="5"/>
     </row>
     <row r="105" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D105" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E105" t="str">
         <f>_xlfn.CONCAT("'MODIS_NPP_2050_R4@1'*(((2020_LC_is_cropland@1=1)*(",I102,")))*(",I98,")*(",I99,")*(",I100,")")</f>
@@ -1647,7 +1759,7 @@
     </row>
     <row r="106" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D106" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E106" t="str">
         <f>_xlfn.CONCAT("'MODIS_NPP_2050_R8@1'*(((2020_LC_is_cropland@1=1)*(",I102,")))*(",I98,")*(",I99,")*(",I100,")")</f>
@@ -1656,20 +1768,20 @@
     </row>
     <row r="108" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D108" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E108" t="s">
         <v>40</v>
-      </c>
-      <c r="E108" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="109" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D109" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="110" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D110" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
